--- a/docs/ValueSet-VSVFYesNo.xlsx
+++ b/docs/ValueSet-VSVFYesNo.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-08T21:21:15+00:00</t>
+    <t>2023-11-08T21:56:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFYesNo.xlsx
+++ b/docs/ValueSet-VSVFYesNo.xlsx
@@ -23,13 +23,13 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ValueSet/VFYesNo</t>
+    <t>http://va.gov/fhir/ValueSet/VSVFYesNo</t>
   </si>
   <si>
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.3.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-08T21:56:35+00:00</t>
+    <t>2023-11-09T22:38:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFYesNo.xlsx
+++ b/docs/ValueSet-VSVFYesNo.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-09T22:38:39+00:00</t>
+    <t>2023-11-14T14:54:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFYesNo.xlsx
+++ b/docs/ValueSet-VSVFYesNo.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-14T14:54:31+00:00</t>
+    <t>2023-11-14T17:25:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFYesNo.xlsx
+++ b/docs/ValueSet-VSVFYesNo.xlsx
@@ -29,7 +29,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.3.0</t>
+    <t>0.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-14T17:25:19+00:00</t>
+    <t>2023-11-15T12:04:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFYesNo.xlsx
+++ b/docs/ValueSet-VSVFYesNo.xlsx
@@ -29,7 +29,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.4.0</t>
+    <t>0.5.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-15T12:04:59+00:00</t>
+    <t>2023-11-15T19:14:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFYesNo.xlsx
+++ b/docs/ValueSet-VSVFYesNo.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-15T19:14:31+00:00</t>
+    <t>2023-11-15T20:37:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFYesNo.xlsx
+++ b/docs/ValueSet-VSVFYesNo.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-15T20:37:43+00:00</t>
+    <t>2023-11-29T20:32:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -80,7 +80,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>ValueSet VF_YesNo</t>
+    <t>Use the link in the Expansion section to navigate to the ConceptMap.</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/ValueSet-VSVFYesNo.xlsx
+++ b/docs/ValueSet-VSVFYesNo.xlsx
@@ -29,7 +29,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.0</t>
+    <t>0.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-29T20:32:59+00:00</t>
+    <t>2023-11-29T21:08:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/ValueSet-VSVFYesNo.xlsx
+++ b/docs/ValueSet-VSVFYesNo.xlsx
@@ -29,7 +29,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-29T21:08:10+00:00</t>
+    <t>2023-12-12T19:04:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
